--- a/artfynd/A 10178-2024 artfynd.xlsx
+++ b/artfynd/A 10178-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>115402757</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,7 +710,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sävemossen (Sävemossen), Sm</t>
+          <t>Sävemossen, Sävemossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -778,6 +773,379 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113980971</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gejmån, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>586676</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6332319</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-03-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Samuel Holdar</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Håkan Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>EEN0068 Gejmån-Ajaure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>98535850</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grönskogen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>586564</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6332457</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-08-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-08-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:56</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>98537922</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grönskogen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>586619</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6332433</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10178-2024 artfynd.xlsx
+++ b/artfynd/A 10178-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115402757</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>EEN0068 Gejmån-Ajaure</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113980971</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98535850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,8 +1166,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98537922</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>